--- a/data/file_generation/input/data_211/总分(物理)_各班学生成绩(方向名次).xlsx
+++ b/data/file_generation/input/data_211/总分(物理)_各班学生成绩(方向名次).xlsx
@@ -71869,18 +71869,26 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
+  <documentManagement>
+    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+  </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CCBAD22-B171-48CC-A521-CB6469FDC1C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{309197E8-2296-4F63-BE87-C6D2003AD3BB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{815895CD-6261-4B7A-9F9E-256B49AF04AA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19D512F5-D36C-4A41-BA01-F0A23B585EF6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24B72784-F2E7-4D88-A5B6-DA6452906BE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAEE2D03-111A-4222-8451-3012B6F19FB5}"/>
 </file>